--- a/Plantilla-TT-SPAC.xlsx
+++ b/Plantilla-TT-SPAC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>ATTRAPI · TT — Subdirección de Procesos Administrativos de Construcción</t>
   </si>
@@ -46,7 +46,7 @@
     <t>SPAC-001</t>
   </si>
   <si>
-    <t>R. Sánchez</t>
+    <t>Mario</t>
   </si>
   <si>
     <t>Formalización contrato segmento 15A1 Saltillo-N. Laredo</t>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>SPAC-002</t>
-  </si>
-  <si>
-    <t>J. R. García</t>
   </si>
   <si>
     <t>Acto de fallo segmento 15A2 Saltillo-N. Laredo</t>
@@ -683,45 +680,45 @@
         <v>17</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>22</v>
       </c>
       <c r="G5" s="10">
         <v>46129.25</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="G6" s="7">
         <v>46149.25</v>

--- a/Plantilla-TT-SPAC.xlsx
+++ b/Plantilla-TT-SPAC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>ATTRAPI · TT — Subdirección de Procesos Administrativos de Construcción</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Estatus</t>
   </si>
   <si>
+    <t>URL</t>
+  </si>
+  <si>
     <t>SPAC-001</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
   </si>
   <si>
     <t>En Proceso</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>SPAC-002</t>
@@ -587,7 +593,7 @@
     <tabColor rgb="FF1E3A8A"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -597,9 +603,10 @@
     <col min="5" max="6" width="38" style="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
+    <col min="9" max="9" width="32" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -610,8 +617,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -622,8 +630,9 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-    </row>
-    <row r="3" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -648,86 +657,98 @@
       <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="7">
         <v>46152.25</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G5" s="10">
         <v>46129.25</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G6" s="7">
         <v>46149.25</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -736,8 +757,9 @@
       <c r="F7" s="9"/>
       <c r="G7" s="10"/>
       <c r="H7" s="11"/>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -746,8 +768,9 @@
       <c r="F8" s="6"/>
       <c r="G8" s="7"/>
       <c r="H8" s="8"/>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -756,8 +779,9 @@
       <c r="F9" s="9"/>
       <c r="G9" s="10"/>
       <c r="H9" s="11"/>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -766,8 +790,9 @@
       <c r="F10" s="6"/>
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -776,8 +801,9 @@
       <c r="F11" s="9"/>
       <c r="G11" s="10"/>
       <c r="H11" s="11"/>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -786,8 +812,9 @@
       <c r="F12" s="6"/>
       <c r="G12" s="7"/>
       <c r="H12" s="8"/>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -796,8 +823,9 @@
       <c r="F13" s="9"/>
       <c r="G13" s="10"/>
       <c r="H13" s="11"/>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -806,8 +834,9 @@
       <c r="F14" s="6"/>
       <c r="G14" s="7"/>
       <c r="H14" s="8"/>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="6"/>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -816,8 +845,9 @@
       <c r="F15" s="9"/>
       <c r="G15" s="10"/>
       <c r="H15" s="11"/>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -826,8 +856,9 @@
       <c r="F16" s="6"/>
       <c r="G16" s="7"/>
       <c r="H16" s="8"/>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" s="6"/>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -836,8 +867,9 @@
       <c r="F17" s="9"/>
       <c r="G17" s="10"/>
       <c r="H17" s="11"/>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" s="9"/>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -846,8 +878,9 @@
       <c r="F18" s="6"/>
       <c r="G18" s="7"/>
       <c r="H18" s="8"/>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="6"/>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -856,8 +889,9 @@
       <c r="F19" s="9"/>
       <c r="G19" s="10"/>
       <c r="H19" s="11"/>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" s="9"/>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -866,8 +900,9 @@
       <c r="F20" s="6"/>
       <c r="G20" s="7"/>
       <c r="H20" s="8"/>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -876,8 +911,9 @@
       <c r="F21" s="9"/>
       <c r="G21" s="10"/>
       <c r="H21" s="11"/>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" s="9"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -886,8 +922,9 @@
       <c r="F22" s="6"/>
       <c r="G22" s="7"/>
       <c r="H22" s="8"/>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -896,8 +933,9 @@
       <c r="F23" s="9"/>
       <c r="G23" s="10"/>
       <c r="H23" s="11"/>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23" s="9"/>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -906,8 +944,9 @@
       <c r="F24" s="6"/>
       <c r="G24" s="7"/>
       <c r="H24" s="8"/>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -916,8 +955,9 @@
       <c r="F25" s="9"/>
       <c r="G25" s="10"/>
       <c r="H25" s="11"/>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" s="9"/>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -926,8 +966,9 @@
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
       <c r="H26" s="8"/>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -936,8 +977,9 @@
       <c r="F27" s="9"/>
       <c r="G27" s="10"/>
       <c r="H27" s="11"/>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -946,11 +988,12 @@
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
       <c r="H28" s="8"/>
+      <c r="I28" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" showErrorMessage="1" errorTitle="Estatus inválido" error="Selecciona En Proceso o Atendida" sqref="H10:H28">

--- a/Plantilla-TT-SPAC.xlsx
+++ b/Plantilla-TT-SPAC.xlsx
@@ -49,7 +49,7 @@
     <t>SPAC-001</t>
   </si>
   <si>
-    <t>Mario</t>
+    <t>MARIO</t>
   </si>
   <si>
     <t>Formalización contrato segmento 15A1 Saltillo-N. Laredo</t>
